--- a/config/excel/chapters.xlsx
+++ b/config/excel/chapters.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="chapters" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -423,13 +423,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -482,11 +482,29 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
           <t>Boss 与高强度混合战</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>第三章</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>新怪种逐步登场，终局对战千足虫</t>
         </is>
       </c>
     </row>
